--- a/samples/mapped_payroll_columns.xlsx
+++ b/samples/mapped_payroll_columns.xlsx
@@ -415,27 +415,23 @@
   </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>record type</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>column name</t>
+          <t>Column Name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -447,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -459,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
